--- a/business_forms/027_program_quality_survey--business_forms.xlsx
+++ b/business_forms/027_program_quality_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_title</t>
+          <t>overall_quality</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey Title</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall Quality</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This question is to gauge your overall perception of the program.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>service_quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Service Quality</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>How would you rate the quality of service offered by this program?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>staff_responsiveness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How would you rate the responsiveness of staff?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Staff Responsiveness</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How responsive are the staff of the program?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>communication_quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How would you rate the communication from the staff?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Communication Quality</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How would you rate the communication from the program's staff?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>program_improvement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How would you rate the overall quality of the program?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Improvement Suggestions</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What could the program do to improve?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>likes_dislikes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What could the program do to improve?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Likes/Dislikes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What did you like or dislike about the program?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>expectations_met</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Expectations Met</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Is this program meeting your expectations?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>visits_count</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Visits Count</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>How many times have you visited this program?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Recommendations</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>How many times would you recommend this program to others?</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>staff_knowledge</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How would you rate the program staff's knowledge of the subject matter?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Staff Knowledge</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How would you rate the program's staff knowledge of the subject matter?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>responsiveness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>How would you rate the program's responsiveness to suggestions?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>program_quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How would you rate the program's communication with you?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Overall Quality Again</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>How would you rate the program's overall quality?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_12</t>
+          <t>staff_friendly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate the program's overall quality?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Staff Friendliness</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Is the program staff friendly?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,41 +871,49 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_13</t>
+          <t>open_ended_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Open-Ended 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>What could the program do to improve?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_14</t>
+          <t>open_ended_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Is this program meeting your expectations?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Open-Ended 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Is there anything else you would like to add about this program?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_15</t>
+          <t>overall_opinion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How many times have you visited this program?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Overall Opinion</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>What is your overall opinion of this program?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,223 +952,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_16</t>
+          <t>last_question</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many times would you recommend this program to others?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Last Question</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Any other comments or suggestions?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What did you like about this program?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What did you dislike about this program?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Is there anything else you would like to add about this program?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you have any suggestions for improvement?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your overall opinion of this program?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Is the program staff friendly?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How would you rate the program's overall quality?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What could the program do to improve?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Is this program meeting your expectations?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,10 +982,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1149,7 +1010,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1166,7 +1027,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1183,7 +1044,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1200,7 +1061,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>overall_quality_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1217,7 +1078,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>service_quality_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1234,7 +1095,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>service_quality_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1251,7 +1112,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>service_quality_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1268,7 +1129,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>service_quality_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1285,7 +1146,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>staff_responsiveness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,7 +1163,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>staff_responsiveness_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1319,7 +1180,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>staff_responsiveness_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1336,7 +1197,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>staff_responsiveness_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1353,7 +1214,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>communication_quality_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1370,7 +1231,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>communication_quality_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1387,7 +1248,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>communication_quality_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1404,7 +1265,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>communication_quality_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1421,7 +1282,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>expectations_met_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1438,7 +1299,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>expectations_met_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1455,7 +1316,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>staff_knowledge_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1472,7 +1333,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>staff_knowledge_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1489,7 +1350,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>staff_knowledge_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1506,7 +1367,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>staff_knowledge_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1523,7 +1384,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>responsiveness_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1540,7 +1401,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>responsiveness_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1557,7 +1418,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>responsiveness_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1574,7 +1435,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>responsiveness_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1591,7 +1452,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>program_quality_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1608,7 +1469,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>program_quality_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1625,7 +1486,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>program_quality_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1642,7 +1503,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>program_quality_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1659,236 +1520,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>staff_friendly_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>staff_friendly_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>question_14_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>question_14_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>False</t>
         </is>
